--- a/Locks_and_deferred.xlsx
+++ b/Locks_and_deferred.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cesar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA68534A-CE5F-434D-83F1-10C917DCA793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6826CA6E-251A-4895-AB7E-CE97F6567672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Locks_and_deferred.xlsx
+++ b/Locks_and_deferred.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cesar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cesar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6826CA6E-251A-4895-AB7E-CE97F6567672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D63A9F-5B2A-45B6-9608-F380C33D8DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aircraft" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11250" uniqueCount="2907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11107" uniqueCount="2902">
   <si>
     <t>Aircraft_Registration</t>
   </si>
@@ -8120,25 +8120,10 @@
     <t>Document_Revision</t>
   </si>
   <si>
-    <t>Manual_Table</t>
-  </si>
-  <si>
     <t>Main</t>
   </si>
   <si>
     <t>Side-by-Side</t>
-  </si>
-  <si>
-    <t>Centerline</t>
-  </si>
-  <si>
-    <t>Ambos</t>
-  </si>
-  <si>
-    <t>Lower</t>
-  </si>
-  <si>
-    <t>Standard</t>
   </si>
   <si>
     <t>Rule_ID</t>
@@ -9394,7 +9379,7 @@
     <col min="13" max="13" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -9423,45 +9408,42 @@
         <v>2688</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2689</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2690</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>2381</v>
-      </c>
-      <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E2" s="4">
-        <v>3701</v>
+        <v>2073</v>
       </c>
       <c r="F2" s="4">
-        <v>1746</v>
+        <v>1036</v>
       </c>
       <c r="G2" s="4">
-        <v>1747</v>
+        <v>1036</v>
       </c>
       <c r="H2" s="4">
-        <v>1760</v>
+        <v>1100</v>
       </c>
       <c r="I2" s="4">
-        <v>1916</v>
+        <v>1100</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9469,13 +9451,13 @@
         <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E3" s="4">
         <v>3701</v>
@@ -9487,10 +9469,13 @@
         <v>1747</v>
       </c>
       <c r="H3" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I3" s="4">
         <v>1916</v>
       </c>
-      <c r="I3" s="4">
-        <v>1968</v>
+      <c r="J3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9498,13 +9483,13 @@
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E4" s="4">
         <v>3701</v>
@@ -9516,10 +9501,13 @@
         <v>1747</v>
       </c>
       <c r="H4" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I4" s="4">
-        <v>1916</v>
+        <v>1968</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9527,13 +9515,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E5" s="4">
         <v>3701</v>
@@ -9545,10 +9533,13 @@
         <v>1747</v>
       </c>
       <c r="H5" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I5" s="4">
         <v>1916</v>
       </c>
-      <c r="I5" s="4">
-        <v>1968</v>
+      <c r="J5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9556,13 +9547,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E6" s="4">
         <v>3701</v>
@@ -9574,10 +9565,13 @@
         <v>1747</v>
       </c>
       <c r="H6" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I6" s="4">
-        <v>1916</v>
+        <v>1968</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9585,13 +9579,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E7" s="4">
         <v>3701</v>
@@ -9603,10 +9597,13 @@
         <v>1747</v>
       </c>
       <c r="H7" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I7" s="4">
         <v>1916</v>
       </c>
-      <c r="I7" s="4">
-        <v>1968</v>
+      <c r="J7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9614,13 +9611,13 @@
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E8" s="4">
         <v>3701</v>
@@ -9632,10 +9629,13 @@
         <v>1747</v>
       </c>
       <c r="H8" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I8" s="4">
-        <v>1916</v>
+        <v>1968</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9643,13 +9643,13 @@
         <v>13</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E9" s="4">
         <v>3701</v>
@@ -9661,10 +9661,13 @@
         <v>1747</v>
       </c>
       <c r="H9" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I9" s="4">
         <v>1916</v>
       </c>
-      <c r="I9" s="4">
-        <v>1968</v>
+      <c r="J9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9672,28 +9675,31 @@
         <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E10" s="4">
-        <v>5225</v>
+        <v>3701</v>
       </c>
       <c r="F10" s="4">
-        <v>2466</v>
+        <v>1746</v>
       </c>
       <c r="G10" s="4">
-        <v>2400</v>
+        <v>1747</v>
       </c>
       <c r="H10" s="4">
-        <v>3076</v>
+        <v>1916</v>
       </c>
       <c r="I10" s="4">
-        <v>2890</v>
+        <v>1968</v>
+      </c>
+      <c r="J10" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9701,28 +9707,31 @@
         <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E11" s="4">
-        <v>5225</v>
+        <v>3701</v>
       </c>
       <c r="F11" s="4">
-        <v>2466</v>
+        <v>1746</v>
       </c>
       <c r="G11" s="4">
-        <v>2400</v>
+        <v>1747</v>
       </c>
       <c r="H11" s="4">
-        <v>2962</v>
+        <v>1760</v>
       </c>
       <c r="I11" s="4">
-        <v>3077</v>
+        <v>1916</v>
+      </c>
+      <c r="J11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9730,28 +9739,31 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E12" s="4">
-        <v>5225</v>
+        <v>3701</v>
       </c>
       <c r="F12" s="4">
-        <v>2466</v>
+        <v>1746</v>
       </c>
       <c r="G12" s="4">
-        <v>2400</v>
+        <v>1747</v>
       </c>
       <c r="H12" s="4">
-        <v>3076</v>
+        <v>1916</v>
       </c>
       <c r="I12" s="4">
-        <v>2890</v>
+        <v>1968</v>
+      </c>
+      <c r="J12" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9759,28 +9771,31 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E13" s="4">
-        <v>5225</v>
+        <v>3701</v>
       </c>
       <c r="F13" s="4">
-        <v>2466</v>
+        <v>1746</v>
       </c>
       <c r="G13" s="4">
-        <v>2400</v>
+        <v>1747</v>
       </c>
       <c r="H13" s="4">
-        <v>2962</v>
+        <v>1760</v>
       </c>
       <c r="I13" s="4">
-        <v>3077</v>
+        <v>1916</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9788,13 +9803,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E14" s="4">
         <v>3701</v>
@@ -9806,10 +9821,13 @@
         <v>1747</v>
       </c>
       <c r="H14" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I14" s="4">
-        <v>1916</v>
+        <v>1968</v>
+      </c>
+      <c r="J14" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9817,13 +9835,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E15" s="4">
         <v>3701</v>
@@ -9835,10 +9853,13 @@
         <v>1747</v>
       </c>
       <c r="H15" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I15" s="4">
         <v>1916</v>
       </c>
-      <c r="I15" s="4">
-        <v>1968</v>
+      <c r="J15" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9846,13 +9867,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E16" s="4">
         <v>3701</v>
@@ -9864,24 +9885,27 @@
         <v>1747</v>
       </c>
       <c r="H16" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I16" s="4">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E17" s="4">
         <v>3701</v>
@@ -9893,24 +9917,27 @@
         <v>1747</v>
       </c>
       <c r="H17" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I17" s="4">
         <v>1916</v>
       </c>
-      <c r="I17" s="4">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E18" s="4">
         <v>3701</v>
@@ -9922,24 +9949,27 @@
         <v>1747</v>
       </c>
       <c r="H18" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I18" s="4">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E19" s="4">
         <v>3701</v>
@@ -9951,24 +9981,27 @@
         <v>1747</v>
       </c>
       <c r="H19" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I19" s="4">
         <v>1916</v>
       </c>
-      <c r="I19" s="4">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E20" s="4">
         <v>3701</v>
@@ -9980,24 +10013,27 @@
         <v>1747</v>
       </c>
       <c r="H20" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I20" s="4">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E21" s="4">
         <v>3701</v>
@@ -10009,24 +10045,27 @@
         <v>1747</v>
       </c>
       <c r="H21" s="4">
+        <v>1760</v>
+      </c>
+      <c r="I21" s="4">
         <v>1916</v>
       </c>
-      <c r="I21" s="4">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E22" s="4">
         <v>3701</v>
@@ -10038,24 +10077,27 @@
         <v>1747</v>
       </c>
       <c r="H22" s="4">
-        <v>1760</v>
+        <v>1916</v>
       </c>
       <c r="I22" s="4">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E23" s="4">
         <v>3701</v>
@@ -10067,2128 +10109,1363 @@
         <v>1747</v>
       </c>
       <c r="H23" s="4">
+        <v>1997</v>
+      </c>
+      <c r="I23" s="4">
         <v>1916</v>
       </c>
-      <c r="I23" s="4">
+      <c r="J23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E24" s="4">
+        <v>3701</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1746</v>
+      </c>
+      <c r="G24" s="4">
+        <v>1747</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1916</v>
+      </c>
+      <c r="I24" s="4">
         <v>1968</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="J24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>2692</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="D25" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="4">
         <v>2721</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F25" s="4">
         <v>2721</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G25" s="4">
         <v>2721</v>
       </c>
-      <c r="H24" s="4">
-        <v>1451</v>
-      </c>
-      <c r="I24" s="4">
-        <v>2721</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>2692</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F25" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G25" s="4">
-        <v>3855</v>
-      </c>
       <c r="H25" s="4">
-        <v>1814</v>
+        <v>1133</v>
       </c>
       <c r="I25" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1133</v>
+      </c>
+      <c r="J25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>2692</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>131</v>
+      <c r="D26" s="3">
+        <v>1</v>
       </c>
       <c r="E26" s="4">
-        <v>3855</v>
+        <v>2280</v>
       </c>
       <c r="F26" s="4">
-        <v>3855</v>
+        <v>1140</v>
       </c>
       <c r="G26" s="4">
-        <v>3855</v>
+        <v>1140</v>
       </c>
       <c r="H26" s="4">
-        <v>1814</v>
+        <v>1200</v>
       </c>
       <c r="I26" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1200</v>
+      </c>
+      <c r="J26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>141</v>
+        <v>568</v>
       </c>
       <c r="E27" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F27" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G27" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H27" s="4">
-        <v>1814</v>
+        <v>1760</v>
       </c>
       <c r="I27" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>138</v>
+        <v>571</v>
       </c>
       <c r="E28" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F28" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G28" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H28" s="4">
-        <v>1814</v>
+        <v>1916</v>
       </c>
       <c r="I28" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>147</v>
+        <v>574</v>
       </c>
       <c r="E29" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F29" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G29" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H29" s="4">
-        <v>2812</v>
+        <v>1760</v>
       </c>
       <c r="I29" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>144</v>
+        <v>577</v>
       </c>
       <c r="E30" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F30" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G30" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H30" s="4">
-        <v>2812</v>
+        <v>1916</v>
       </c>
       <c r="I30" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>153</v>
+        <v>580</v>
       </c>
       <c r="E31" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F31" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G31" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H31" s="4">
-        <v>2812</v>
+        <v>1760</v>
       </c>
       <c r="I31" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D32" s="3" t="s">
-        <v>150</v>
+        <v>583</v>
       </c>
       <c r="E32" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F32" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G32" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H32" s="4">
-        <v>2812</v>
+        <v>1916</v>
       </c>
       <c r="I32" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>159</v>
+        <v>586</v>
       </c>
       <c r="E33" s="4">
-        <v>6032</v>
+        <v>3701</v>
       </c>
       <c r="F33" s="4">
-        <v>5488</v>
+        <v>1746</v>
       </c>
       <c r="G33" s="4">
-        <v>5488</v>
+        <v>1747</v>
       </c>
       <c r="H33" s="4">
-        <v>3855</v>
+        <v>1760</v>
       </c>
       <c r="I33" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>156</v>
+        <v>589</v>
       </c>
       <c r="E34" s="4">
-        <v>6032</v>
+        <v>3701</v>
       </c>
       <c r="F34" s="4">
-        <v>5488</v>
+        <v>1746</v>
       </c>
       <c r="G34" s="4">
-        <v>5488</v>
+        <v>1747</v>
       </c>
       <c r="H34" s="4">
-        <v>3855</v>
+        <v>1916</v>
       </c>
       <c r="I34" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>165</v>
+        <v>592</v>
       </c>
       <c r="E35" s="4">
-        <v>6032</v>
+        <v>3701</v>
       </c>
       <c r="F35" s="4">
-        <v>5488</v>
+        <v>1746</v>
       </c>
       <c r="G35" s="4">
-        <v>5488</v>
+        <v>1747</v>
       </c>
       <c r="H35" s="4">
-        <v>3855</v>
+        <v>1760</v>
       </c>
       <c r="I35" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>162</v>
+        <v>595</v>
       </c>
       <c r="E36" s="4">
-        <v>6032</v>
+        <v>3701</v>
       </c>
       <c r="F36" s="4">
-        <v>5488</v>
+        <v>1746</v>
       </c>
       <c r="G36" s="4">
-        <v>5488</v>
+        <v>1747</v>
       </c>
       <c r="H36" s="4">
-        <v>3855</v>
+        <v>1916</v>
       </c>
       <c r="I36" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>171</v>
+        <v>598</v>
       </c>
       <c r="E37" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F37" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G37" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H37" s="4">
-        <v>2131</v>
+        <v>1760</v>
       </c>
       <c r="I37" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>168</v>
+        <v>601</v>
       </c>
       <c r="E38" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F38" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G38" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H38" s="4">
-        <v>2131</v>
+        <v>1916</v>
       </c>
       <c r="I38" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>177</v>
+        <v>604</v>
       </c>
       <c r="E39" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F39" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G39" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H39" s="4">
-        <v>2131</v>
+        <v>1760</v>
       </c>
       <c r="I39" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>174</v>
+        <v>607</v>
       </c>
       <c r="E40" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F40" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G40" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H40" s="4">
-        <v>2131</v>
+        <v>1916</v>
       </c>
       <c r="I40" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>183</v>
+        <v>610</v>
       </c>
       <c r="E41" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F41" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G41" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H41" s="4">
-        <v>2131</v>
+        <v>1760</v>
       </c>
       <c r="I41" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>180</v>
+        <v>613</v>
       </c>
       <c r="E42" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F42" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G42" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H42" s="4">
-        <v>2131</v>
+        <v>1916</v>
       </c>
       <c r="I42" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>189</v>
+        <v>616</v>
       </c>
       <c r="E43" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F43" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G43" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H43" s="4">
-        <v>2766</v>
+        <v>1760</v>
       </c>
       <c r="I43" s="4">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>186</v>
+        <v>619</v>
       </c>
       <c r="E44" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F44" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G44" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H44" s="4">
-        <v>2766</v>
+        <v>1916</v>
       </c>
       <c r="I44" s="4">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>195</v>
+        <v>442</v>
       </c>
       <c r="E45" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F45" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G45" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H45" s="4">
-        <v>2766</v>
+        <v>1760</v>
       </c>
       <c r="I45" s="4">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>192</v>
+        <v>447</v>
       </c>
       <c r="E46" s="4">
-        <v>3855</v>
+        <v>3701</v>
       </c>
       <c r="F46" s="4">
-        <v>3855</v>
+        <v>1746</v>
       </c>
       <c r="G46" s="4">
-        <v>3855</v>
+        <v>1747</v>
       </c>
       <c r="H46" s="4">
-        <v>2766</v>
+        <v>1916</v>
       </c>
       <c r="I46" s="4">
-        <v>2766</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>2692</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>198</v>
+        <v>450</v>
       </c>
       <c r="E47" s="4">
-        <v>2721</v>
+        <v>3701</v>
       </c>
       <c r="F47" s="4">
-        <v>2721</v>
+        <v>1746</v>
       </c>
       <c r="G47" s="4">
-        <v>2721</v>
+        <v>1747</v>
       </c>
       <c r="H47" s="4">
-        <v>1133</v>
+        <v>1850</v>
       </c>
       <c r="I47" s="4">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1916</v>
+      </c>
+      <c r="J47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D48" s="3">
-        <v>1</v>
+      <c r="D48" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="E48" s="4">
-        <v>2721</v>
+        <v>3701</v>
       </c>
       <c r="F48" s="4">
-        <v>2721</v>
+        <v>1746</v>
       </c>
       <c r="G48" s="4">
-        <v>2721</v>
+        <v>1747</v>
       </c>
       <c r="H48" s="4">
-        <v>1451</v>
+        <v>1916</v>
       </c>
       <c r="I48" s="4">
-        <v>2721</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1968</v>
+      </c>
+      <c r="J48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>2691</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>568</v>
+      <c r="D49" s="3">
+        <v>17</v>
       </c>
       <c r="E49" s="4">
-        <v>3855</v>
+        <v>2721</v>
       </c>
       <c r="F49" s="4">
-        <v>3855</v>
+        <v>2721</v>
       </c>
       <c r="G49" s="4">
-        <v>3855</v>
+        <v>2721</v>
       </c>
       <c r="H49" s="4">
-        <v>1814</v>
+        <v>1133</v>
       </c>
       <c r="I49" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="E50" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F50" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G50" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H50" s="4">
-        <v>1814</v>
-      </c>
-      <c r="I50" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E51" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F51" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G51" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H51" s="4">
-        <v>1814</v>
-      </c>
-      <c r="I51" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="E52" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F52" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G52" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H52" s="4">
-        <v>1814</v>
-      </c>
-      <c r="I52" s="4">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="E53" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F53" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G53" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H53" s="4">
-        <v>2812</v>
-      </c>
-      <c r="I53" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="E54" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F54" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G54" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H54" s="4">
-        <v>2812</v>
-      </c>
-      <c r="I54" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="E55" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F55" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G55" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H55" s="4">
-        <v>2812</v>
-      </c>
-      <c r="I55" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="E56" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F56" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G56" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H56" s="4">
-        <v>2812</v>
-      </c>
-      <c r="I56" s="4">
-        <v>2812</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="E57" s="4">
-        <v>6032</v>
-      </c>
-      <c r="F57" s="4">
-        <v>5488</v>
-      </c>
-      <c r="G57" s="4">
-        <v>5488</v>
-      </c>
-      <c r="H57" s="4">
-        <v>3855</v>
-      </c>
-      <c r="I57" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="E58" s="4">
-        <v>6032</v>
-      </c>
-      <c r="F58" s="4">
-        <v>5488</v>
-      </c>
-      <c r="G58" s="4">
-        <v>5488</v>
-      </c>
-      <c r="H58" s="4">
-        <v>3855</v>
-      </c>
-      <c r="I58" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="E59" s="4">
-        <v>6032</v>
-      </c>
-      <c r="F59" s="4">
-        <v>5488</v>
-      </c>
-      <c r="G59" s="4">
-        <v>5488</v>
-      </c>
-      <c r="H59" s="4">
-        <v>3855</v>
-      </c>
-      <c r="I59" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="E60" s="4">
-        <v>6032</v>
-      </c>
-      <c r="F60" s="4">
-        <v>5488</v>
-      </c>
-      <c r="G60" s="4">
-        <v>5488</v>
-      </c>
-      <c r="H60" s="4">
-        <v>3855</v>
-      </c>
-      <c r="I60" s="4">
-        <v>3855</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="E61" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F61" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G61" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H61" s="4">
-        <v>2131</v>
-      </c>
-      <c r="I61" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="E62" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F62" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G62" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H62" s="4">
-        <v>2131</v>
-      </c>
-      <c r="I62" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="E63" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F63" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G63" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H63" s="4">
-        <v>2131</v>
-      </c>
-      <c r="I63" s="4">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E64" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F64" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G64" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H64" s="4">
-        <v>2131</v>
-      </c>
-      <c r="I64" s="4">
-        <v>2131</v>
-      </c>
+        <v>1133</v>
+      </c>
+      <c r="J49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+    </row>
+    <row r="63" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="E65" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F65" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G65" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H65" s="4">
-        <v>2131</v>
-      </c>
-      <c r="I65" s="4">
-        <v>2131</v>
-      </c>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="E66" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F66" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G66" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H66" s="4">
-        <v>2131</v>
-      </c>
-      <c r="I66" s="4">
-        <v>2131</v>
-      </c>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="E67" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F67" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G67" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H67" s="4">
-        <v>2766</v>
-      </c>
-      <c r="I67" s="4">
-        <v>2766</v>
-      </c>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="E68" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F68" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G68" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H68" s="4">
-        <v>2766</v>
-      </c>
-      <c r="I68" s="4">
-        <v>2766</v>
-      </c>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E69" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F69" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G69" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H69" s="4">
-        <v>2766</v>
-      </c>
-      <c r="I69" s="4">
-        <v>2766</v>
-      </c>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="E70" s="4">
-        <v>3855</v>
-      </c>
-      <c r="F70" s="4">
-        <v>3855</v>
-      </c>
-      <c r="G70" s="4">
-        <v>3855</v>
-      </c>
-      <c r="H70" s="4">
-        <v>2766</v>
-      </c>
-      <c r="I70" s="4">
-        <v>2766</v>
-      </c>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E71" s="1">
-        <v>2721</v>
-      </c>
-      <c r="F71" s="1">
-        <v>2721</v>
-      </c>
-      <c r="G71" s="1">
-        <v>2721</v>
-      </c>
-      <c r="H71" s="1">
-        <v>1133</v>
-      </c>
-      <c r="I71" s="1">
-        <v>1133</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E72" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F72" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G72" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H72" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I72" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E73" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F73" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G73" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H73" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I73" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E74" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F74" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G74" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H74" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I74" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E75" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F75" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G75" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H75" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I75" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E76" s="1">
-        <v>6803</v>
-      </c>
-      <c r="F76" s="1">
-        <v>3233</v>
-      </c>
-      <c r="G76" s="1">
-        <v>3234</v>
-      </c>
-      <c r="H76" s="1">
-        <v>3752</v>
-      </c>
-      <c r="I76" s="1">
-        <v>3752</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E77" s="1">
-        <v>6803</v>
-      </c>
-      <c r="F77" s="1">
-        <v>3233</v>
-      </c>
-      <c r="G77" s="1">
-        <v>3234</v>
-      </c>
-      <c r="H77" s="1">
-        <v>3752</v>
-      </c>
-      <c r="I77" s="1">
-        <v>3752</v>
-      </c>
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E78" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F78" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G78" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H78" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I78" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E79" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F79" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G79" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H79" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I79" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E80" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F80" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G80" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H80" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I80" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E81" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F81" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G81" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H81" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I81" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
     </row>
     <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E82" s="1">
-        <v>4819</v>
-      </c>
-      <c r="F82" s="1">
-        <v>2290</v>
-      </c>
-      <c r="G82" s="1">
-        <v>2290</v>
-      </c>
-      <c r="H82" s="1">
-        <v>2494</v>
-      </c>
-      <c r="I82" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
     </row>
     <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E83" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F83" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G83" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H83" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I83" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E84" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F84" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G84" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H84" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I84" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="E85" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F85" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G85" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H85" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I85" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="E86" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F86" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G86" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H86" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I86" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E87" s="1">
-        <v>6803</v>
-      </c>
-      <c r="F87" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G87" s="1">
-        <v>6803</v>
-      </c>
-      <c r="H87" s="1">
-        <v>2766</v>
-      </c>
-      <c r="I87" s="1">
-        <v>2766</v>
-      </c>
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="E88" s="1">
-        <v>6803</v>
-      </c>
-      <c r="F88" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G88" s="1">
-        <v>6803</v>
-      </c>
-      <c r="H88" s="1">
-        <v>2766</v>
-      </c>
-      <c r="I88" s="1">
-        <v>2766</v>
-      </c>
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="E89" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F89" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G89" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H89" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I89" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
     </row>
     <row r="90" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E90" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F90" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G90" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H90" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I90" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
     </row>
     <row r="91" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="E91" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F91" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G91" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H91" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I91" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
     </row>
     <row r="92" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="E92" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F92" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G92" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H92" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I92" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
     </row>
     <row r="93" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>2691</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E93" s="1">
-        <v>5429</v>
-      </c>
-      <c r="F93" s="1">
-        <v>4354</v>
-      </c>
-      <c r="G93" s="1">
-        <v>5429</v>
-      </c>
-      <c r="H93" s="1">
-        <v>2585</v>
-      </c>
-      <c r="I93" s="1">
-        <v>2585</v>
-      </c>
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
     </row>
     <row r="94" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>2694</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>2695</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>2696</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E94" s="1">
-        <v>6032</v>
-      </c>
-      <c r="F94" s="1">
-        <v>3542</v>
-      </c>
-      <c r="G94" s="1">
-        <v>3542</v>
-      </c>
-      <c r="H94" s="1">
-        <v>5102</v>
-      </c>
-      <c r="I94" s="1">
-        <v>4336</v>
-      </c>
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
     </row>
     <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
-        <v>2694</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>2695</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>2696</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="E95" s="1">
-        <v>5987</v>
-      </c>
-      <c r="F95" s="1">
-        <v>1950</v>
-      </c>
-      <c r="G95" s="1">
-        <v>2449</v>
-      </c>
-      <c r="H95" s="1">
-        <v>2993</v>
-      </c>
-      <c r="I95" s="1">
-        <v>2494</v>
-      </c>
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
     </row>
     <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>2694</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>2695</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>2696</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="E96" s="1">
-        <v>5896</v>
-      </c>
-      <c r="F96" s="1">
-        <v>2857</v>
-      </c>
-      <c r="G96" s="1">
-        <v>5896</v>
-      </c>
-      <c r="H96" s="1">
-        <v>4762</v>
-      </c>
-      <c r="I96" s="1">
-        <v>5896</v>
-      </c>
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12217,9 +11494,9 @@
     <col min="12" max="12" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>2697</v>
+        <v>2692</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -12228,19 +11505,19 @@
         <v>2377</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2699</v>
+        <v>2694</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2701</v>
+        <v>2696</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>2354</v>
@@ -12255,24 +11532,24 @@
         <v>2</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>2703</v>
+        <v>2698</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>2705</v>
+        <v>2700</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>2706</v>
+        <v>2701</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2708</v>
+        <v>2703</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
@@ -12281,13 +11558,13 @@
         <v>2382</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2709</v>
+        <v>2704</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>133</v>
@@ -12302,7 +11579,7 @@
         <v>357</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>2712</v>
+        <v>2707</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>133</v>
@@ -12311,10 +11588,10 @@
         <v>4853</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>126</v>
@@ -12325,7 +11602,7 @@
     </row>
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -12334,13 +11611,13 @@
         <v>2388</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2716</v>
+        <v>2711</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>2717</v>
+        <v>2712</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>2718</v>
+        <v>2713</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>133</v>
@@ -12355,7 +11632,7 @@
         <v>357</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>2719</v>
+        <v>2714</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>133</v>
@@ -12364,10 +11641,10 @@
         <v>4164</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>2720</v>
+        <v>2715</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>126</v>
@@ -12378,20 +11655,20 @@
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>2721</v>
+        <v>2716</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>2722</v>
+        <v>2717</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>2724</v>
+        <v>2719</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>126</v>
@@ -12415,10 +11692,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>2726</v>
+        <v>2721</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>126</v>
@@ -12429,20 +11706,20 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>2727</v>
+        <v>2722</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>2728</v>
+        <v>2723</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2729</v>
+        <v>2724</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>2730</v>
+        <v>2725</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>126</v>
@@ -12466,10 +11743,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>2731</v>
+        <v>2726</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>126</v>
@@ -12480,7 +11757,7 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>2732</v>
+        <v>2727</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>12</v>
@@ -12489,13 +11766,13 @@
         <v>2382</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2733</v>
+        <v>2728</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2734</v>
+        <v>2729</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>133</v>
@@ -12510,7 +11787,7 @@
         <v>357</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>133</v>
@@ -12519,7 +11796,7 @@
         <v>4853</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3" t="s">
@@ -12531,7 +11808,7 @@
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>2736</v>
+        <v>2731</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -12540,13 +11817,13 @@
         <v>2382</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2738</v>
+        <v>2733</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>133</v>
@@ -12561,7 +11838,7 @@
         <v>357</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>133</v>
@@ -12570,7 +11847,7 @@
         <v>4853</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3" t="s">
@@ -12582,7 +11859,7 @@
     </row>
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>2739</v>
+        <v>2734</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
@@ -12591,13 +11868,13 @@
         <v>2382</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2740</v>
+        <v>2735</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>133</v>
@@ -12612,7 +11889,7 @@
         <v>357</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>133</v>
@@ -12621,7 +11898,7 @@
         <v>4853</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
@@ -12633,7 +11910,7 @@
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>2742</v>
+        <v>2737</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -12642,13 +11919,13 @@
         <v>2382</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2743</v>
+        <v>2738</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>2744</v>
+        <v>2739</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>133</v>
@@ -12663,7 +11940,7 @@
         <v>357</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>133</v>
@@ -12672,7 +11949,7 @@
         <v>4853</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
@@ -12684,7 +11961,7 @@
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>2745</v>
+        <v>2740</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
@@ -12693,13 +11970,13 @@
         <v>2382</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2746</v>
+        <v>2741</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>2747</v>
+        <v>2742</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>2748</v>
+        <v>2743</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>133</v>
@@ -12714,7 +11991,7 @@
         <v>357</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>133</v>
@@ -12723,7 +12000,7 @@
         <v>6804</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
@@ -12735,7 +12012,7 @@
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>2749</v>
+        <v>2744</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>12</v>
@@ -12744,13 +12021,13 @@
         <v>2382</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2750</v>
+        <v>2745</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2751</v>
+        <v>2746</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>2748</v>
+        <v>2743</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>133</v>
@@ -12765,7 +12042,7 @@
         <v>357</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>133</v>
@@ -12774,7 +12051,7 @@
         <v>6804</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
@@ -12786,7 +12063,7 @@
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>2752</v>
+        <v>2747</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
@@ -12795,13 +12072,13 @@
         <v>2382</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2753</v>
+        <v>2748</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2754</v>
+        <v>2749</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>2748</v>
+        <v>2743</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>133</v>
@@ -12816,7 +12093,7 @@
         <v>357</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>133</v>
@@ -12825,7 +12102,7 @@
         <v>6804</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="s">
@@ -12837,7 +12114,7 @@
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>2755</v>
+        <v>2750</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>12</v>
@@ -12846,13 +12123,13 @@
         <v>2382</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2756</v>
+        <v>2751</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>2757</v>
+        <v>2752</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>133</v>
@@ -12867,7 +12144,7 @@
         <v>357</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>133</v>
@@ -12876,7 +12153,7 @@
         <v>4853</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="s">
@@ -12888,7 +12165,7 @@
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>2758</v>
+        <v>2753</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -12897,13 +12174,13 @@
         <v>2382</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2759</v>
+        <v>2754</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>2760</v>
+        <v>2755</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>133</v>
@@ -12918,7 +12195,7 @@
         <v>357</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>133</v>
@@ -12927,7 +12204,7 @@
         <v>4853</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
@@ -12939,7 +12216,7 @@
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>2761</v>
+        <v>2756</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>12</v>
@@ -12948,13 +12225,13 @@
         <v>2382</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2762</v>
+        <v>2757</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2763</v>
+        <v>2758</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>133</v>
@@ -12969,7 +12246,7 @@
         <v>357</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>133</v>
@@ -12978,7 +12255,7 @@
         <v>4853</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
@@ -12990,7 +12267,7 @@
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2764</v>
+        <v>2759</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
@@ -12999,13 +12276,13 @@
         <v>2382</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2765</v>
+        <v>2760</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>2766</v>
+        <v>2761</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>133</v>
@@ -13020,7 +12297,7 @@
         <v>357</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>2735</v>
+        <v>2730</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>133</v>
@@ -13029,7 +12306,7 @@
         <v>4853</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3" t="s">
@@ -13041,7 +12318,7 @@
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>2767</v>
+        <v>2762</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
@@ -13050,13 +12327,13 @@
         <v>2388</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2768</v>
+        <v>2763</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2769</v>
+        <v>2764</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>133</v>
@@ -13071,7 +12348,7 @@
         <v>357</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>133</v>
@@ -13080,7 +12357,7 @@
         <v>4164</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
@@ -13092,7 +12369,7 @@
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>2772</v>
+        <v>2767</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>12</v>
@@ -13101,13 +12378,13 @@
         <v>2388</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2773</v>
+        <v>2768</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>2774</v>
+        <v>2769</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>133</v>
@@ -13122,7 +12399,7 @@
         <v>357</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>133</v>
@@ -13131,7 +12408,7 @@
         <v>4164</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3" t="s">
@@ -13143,7 +12420,7 @@
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>2775</v>
+        <v>2770</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
@@ -13152,13 +12429,13 @@
         <v>2388</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2776</v>
+        <v>2771</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2777</v>
+        <v>2772</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>133</v>
@@ -13173,7 +12450,7 @@
         <v>357</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>133</v>
@@ -13182,7 +12459,7 @@
         <v>4164</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3" t="s">
@@ -13194,7 +12471,7 @@
     </row>
     <row r="20" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>2778</v>
+        <v>2773</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
@@ -13203,13 +12480,13 @@
         <v>2388</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2779</v>
+        <v>2774</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>2780</v>
+        <v>2775</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>133</v>
@@ -13224,7 +12501,7 @@
         <v>357</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>133</v>
@@ -13233,7 +12510,7 @@
         <v>4164</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3" t="s">
@@ -13245,7 +12522,7 @@
     </row>
     <row r="21" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>2781</v>
+        <v>2776</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>12</v>
@@ -13254,13 +12531,13 @@
         <v>2388</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2782</v>
+        <v>2777</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2783</v>
+        <v>2778</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>2784</v>
+        <v>2779</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>133</v>
@@ -13275,7 +12552,7 @@
         <v>357</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>133</v>
@@ -13284,7 +12561,7 @@
         <v>5879</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
@@ -13296,7 +12573,7 @@
     </row>
     <row r="22" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>2785</v>
+        <v>2780</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>12</v>
@@ -13305,13 +12582,13 @@
         <v>2388</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2786</v>
+        <v>2781</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>2787</v>
+        <v>2782</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>2784</v>
+        <v>2779</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>133</v>
@@ -13326,7 +12603,7 @@
         <v>357</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>133</v>
@@ -13335,7 +12612,7 @@
         <v>5879</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
@@ -13347,7 +12624,7 @@
     </row>
     <row r="23" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>2788</v>
+        <v>2783</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
@@ -13356,13 +12633,13 @@
         <v>2388</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2789</v>
+        <v>2784</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>2790</v>
+        <v>2785</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>133</v>
@@ -13377,7 +12654,7 @@
         <v>357</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>133</v>
@@ -13386,7 +12663,7 @@
         <v>4164</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="s">
@@ -13398,7 +12675,7 @@
     </row>
     <row r="24" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>2791</v>
+        <v>2786</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
@@ -13407,13 +12684,13 @@
         <v>2388</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>133</v>
@@ -13428,7 +12705,7 @@
         <v>357</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>133</v>
@@ -13437,7 +12714,7 @@
         <v>4164</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="s">
@@ -13449,7 +12726,7 @@
     </row>
     <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>2794</v>
+        <v>2789</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>12</v>
@@ -13458,13 +12735,13 @@
         <v>2388</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2795</v>
+        <v>2790</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>2796</v>
+        <v>2791</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>133</v>
@@ -13479,7 +12756,7 @@
         <v>357</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>133</v>
@@ -13488,7 +12765,7 @@
         <v>4164</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3" t="s">
@@ -13500,7 +12777,7 @@
     </row>
     <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>2797</v>
+        <v>2792</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>12</v>
@@ -13509,13 +12786,13 @@
         <v>2388</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2798</v>
+        <v>2793</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2799</v>
+        <v>2794</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>133</v>
@@ -13530,7 +12807,7 @@
         <v>357</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>133</v>
@@ -13539,7 +12816,7 @@
         <v>4164</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
@@ -13551,7 +12828,7 @@
     </row>
     <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>2800</v>
+        <v>2795</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>12</v>
@@ -13560,13 +12837,13 @@
         <v>2388</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2801</v>
+        <v>2796</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2802</v>
+        <v>2797</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>133</v>
@@ -13581,7 +12858,7 @@
         <v>357</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>133</v>
@@ -13590,7 +12867,7 @@
         <v>4164</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3" t="s">
@@ -13602,7 +12879,7 @@
     </row>
     <row r="28" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>2803</v>
+        <v>2798</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>12</v>
@@ -13611,13 +12888,13 @@
         <v>2388</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2804</v>
+        <v>2799</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>2805</v>
+        <v>2800</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>133</v>
@@ -13632,7 +12909,7 @@
         <v>357</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>2771</v>
+        <v>2766</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>133</v>
@@ -13641,7 +12918,7 @@
         <v>4164</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3" t="s">
@@ -13653,7 +12930,7 @@
     </row>
     <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>2806</v>
+        <v>2801</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>12</v>
@@ -13662,13 +12939,13 @@
         <v>2382</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2807</v>
+        <v>2802</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>2808</v>
+        <v>2803</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>2809</v>
+        <v>2804</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>126</v>
@@ -13677,13 +12954,13 @@
         <v>1</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="J29" s="3">
         <v>1</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>2811</v>
+        <v>2806</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>133</v>
@@ -13692,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>2812</v>
+        <v>2807</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>126</v>
@@ -13706,7 +12983,7 @@
     </row>
     <row r="30" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>2813</v>
+        <v>2808</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>12</v>
@@ -13715,13 +12992,13 @@
         <v>2388</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2814</v>
+        <v>2809</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>2815</v>
+        <v>2810</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>2809</v>
+        <v>2804</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>126</v>
@@ -13730,13 +13007,13 @@
         <v>1</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="J30" s="3">
         <v>1</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>2811</v>
+        <v>2806</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>133</v>
@@ -13745,10 +13022,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>2812</v>
+        <v>2807</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>126</v>
@@ -13759,22 +13036,22 @@
     </row>
     <row r="31" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>2816</v>
+        <v>2811</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>2817</v>
+        <v>2812</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2818</v>
+        <v>2813</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>2819</v>
+        <v>2814</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>2820</v>
+        <v>2815</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>133</v>
@@ -13783,20 +13060,20 @@
         <v>1</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="J31" s="3">
         <v>1</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>2821</v>
+        <v>2816</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>133</v>
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3" t="s">
-        <v>2817</v>
+        <v>2812</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
@@ -13808,22 +13085,22 @@
     </row>
     <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>2822</v>
+        <v>2817</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2823</v>
+        <v>2818</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>2824</v>
+        <v>2819</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>2825</v>
+        <v>2820</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>133</v>
@@ -13845,10 +13122,10 @@
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>2827</v>
+        <v>2822</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>126</v>
@@ -13859,22 +13136,22 @@
     </row>
     <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>2828</v>
+        <v>2823</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2829</v>
+        <v>2824</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>2830</v>
+        <v>2825</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>2831</v>
+        <v>2826</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>126</v>
@@ -13896,10 +13173,10 @@
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>2827</v>
+        <v>2822</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>126</v>
@@ -13910,22 +13187,22 @@
     </row>
     <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>2832</v>
+        <v>2827</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2833</v>
+        <v>2828</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>2834</v>
+        <v>2829</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>2835</v>
+        <v>2830</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>126</v>
@@ -13947,10 +13224,10 @@
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>2836</v>
+        <v>2831</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>126</v>
@@ -13961,22 +13238,22 @@
     </row>
     <row r="35" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>2837</v>
+        <v>2832</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2838</v>
+        <v>2833</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>2839</v>
+        <v>2834</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>2840</v>
+        <v>2835</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>133</v>
@@ -13998,10 +13275,10 @@
       </c>
       <c r="M35" s="3"/>
       <c r="N35" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>2841</v>
+        <v>2836</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>126</v>
@@ -14012,22 +13289,22 @@
     </row>
     <row r="36" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>2842</v>
+        <v>2837</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2843</v>
+        <v>2838</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>2844</v>
+        <v>2839</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>2845</v>
+        <v>2840</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>133</v>
@@ -14049,10 +13326,10 @@
       </c>
       <c r="M36" s="3"/>
       <c r="N36" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>2827</v>
+        <v>2822</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>126</v>
@@ -14063,22 +13340,22 @@
     </row>
     <row r="37" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>2846</v>
+        <v>2841</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2847</v>
+        <v>2842</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>2848</v>
+        <v>2843</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>2849</v>
+        <v>2844</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>133</v>
@@ -14102,10 +13379,10 @@
         <v>43</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>2850</v>
+        <v>2845</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>126</v>
@@ -14116,22 +13393,22 @@
     </row>
     <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>2851</v>
+        <v>2846</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2852</v>
+        <v>2847</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>2853</v>
+        <v>2848</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>2854</v>
+        <v>2849</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>126</v>
@@ -14155,10 +13432,10 @@
         <v>47627</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>2855</v>
+        <v>2850</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>126</v>
@@ -14191,23 +13468,23 @@
     <col min="9" max="9" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>2856</v>
+        <v>2851</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2857</v>
+        <v>2852</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2858</v>
+        <v>2853</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2859</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>135</v>
@@ -14216,12 +13493,12 @@
         <v>1014</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>131</v>
@@ -14230,12 +13507,12 @@
         <v>1010</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>568</v>
@@ -14244,12 +13521,12 @@
         <v>1014</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>2860</v>
+        <v>2855</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>571</v>
@@ -14258,12 +13535,12 @@
         <v>1010</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>135</v>
@@ -14272,12 +13549,12 @@
         <v>1010</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>212</v>
@@ -14286,12 +13563,12 @@
         <v>1010</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>568</v>
@@ -14300,12 +13577,12 @@
         <v>1010</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>667</v>
@@ -14314,12 +13591,12 @@
         <v>1010</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>131</v>
@@ -14328,12 +13605,12 @@
         <v>1014</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>212</v>
@@ -14342,12 +13619,12 @@
         <v>1014</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>571</v>
@@ -14356,12 +13633,12 @@
         <v>1014</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>667</v>
@@ -14370,12 +13647,12 @@
         <v>1014</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>141</v>
@@ -14384,12 +13661,12 @@
         <v>1014</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>138</v>
@@ -14398,12 +13675,12 @@
         <v>1010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>574</v>
@@ -14412,12 +13689,12 @@
         <v>1014</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>577</v>
@@ -14426,12 +13703,12 @@
         <v>1010</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>2868</v>
+        <v>2863</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>141</v>
@@ -14440,12 +13717,12 @@
         <v>1010</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>2868</v>
+        <v>2863</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>215</v>
@@ -14454,12 +13731,12 @@
         <v>1010</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>2868</v>
+        <v>2863</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>574</v>
@@ -14468,12 +13745,12 @@
         <v>1010</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>2868</v>
+        <v>2863</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>670</v>
@@ -14482,12 +13759,12 @@
         <v>1010</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>2869</v>
+        <v>2864</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>138</v>
@@ -14496,12 +13773,12 @@
         <v>1014</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>2869</v>
+        <v>2864</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>215</v>
@@ -14510,12 +13787,12 @@
         <v>1014</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>2869</v>
+        <v>2864</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>577</v>
@@ -14524,12 +13801,12 @@
         <v>1014</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>2869</v>
+        <v>2864</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>670</v>
@@ -14538,12 +13815,12 @@
         <v>1014</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>147</v>
@@ -14552,12 +13829,12 @@
         <v>1014</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>144</v>
@@ -14566,12 +13843,12 @@
         <v>1010</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>580</v>
@@ -14580,12 +13857,12 @@
         <v>1014</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>2870</v>
+        <v>2865</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>583</v>
@@ -14594,12 +13871,12 @@
         <v>1010</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>2871</v>
+        <v>2866</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>147</v>
@@ -14608,12 +13885,12 @@
         <v>1010</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>2871</v>
+        <v>2866</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>218</v>
@@ -14622,12 +13899,12 @@
         <v>1010</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>2871</v>
+        <v>2866</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>580</v>
@@ -14636,12 +13913,12 @@
         <v>1010</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>2871</v>
+        <v>2866</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>673</v>
@@ -14650,12 +13927,12 @@
         <v>1010</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>2872</v>
+        <v>2867</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>144</v>
@@ -14664,12 +13941,12 @@
         <v>1014</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>2872</v>
+        <v>2867</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>218</v>
@@ -14678,12 +13955,12 @@
         <v>1014</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>2872</v>
+        <v>2867</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>583</v>
@@ -14692,12 +13969,12 @@
         <v>1014</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>2872</v>
+        <v>2867</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>673</v>
@@ -14706,12 +13983,12 @@
         <v>1014</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>2873</v>
+        <v>2868</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>153</v>
@@ -14720,12 +13997,12 @@
         <v>1014</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>2873</v>
+        <v>2868</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>150</v>
@@ -14734,12 +14011,12 @@
         <v>1010</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>2873</v>
+        <v>2868</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>586</v>
@@ -14748,12 +14025,12 @@
         <v>1014</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>2873</v>
+        <v>2868</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>589</v>
@@ -14762,12 +14039,12 @@
         <v>1010</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>2874</v>
+        <v>2869</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>153</v>
@@ -14776,12 +14053,12 @@
         <v>1010</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>2874</v>
+        <v>2869</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>221</v>
@@ -14790,12 +14067,12 @@
         <v>1010</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>2874</v>
+        <v>2869</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>586</v>
@@ -14804,12 +14081,12 @@
         <v>1010</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>2874</v>
+        <v>2869</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>676</v>
@@ -14818,12 +14095,12 @@
         <v>1010</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>2875</v>
+        <v>2870</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>150</v>
@@ -14832,12 +14109,12 @@
         <v>1014</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>2875</v>
+        <v>2870</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>221</v>
@@ -14846,12 +14123,12 @@
         <v>1014</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>2875</v>
+        <v>2870</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>589</v>
@@ -14860,12 +14137,12 @@
         <v>1014</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>2875</v>
+        <v>2870</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>676</v>
@@ -14874,12 +14151,12 @@
         <v>1014</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>2876</v>
+        <v>2871</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>159</v>
@@ -14888,12 +14165,12 @@
         <v>1014</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>2876</v>
+        <v>2871</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>156</v>
@@ -14902,12 +14179,12 @@
         <v>1010</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>2876</v>
+        <v>2871</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>592</v>
@@ -14916,12 +14193,12 @@
         <v>1014</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>2876</v>
+        <v>2871</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>595</v>
@@ -14930,12 +14207,12 @@
         <v>1010</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>2877</v>
+        <v>2872</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>159</v>
@@ -14944,12 +14221,12 @@
         <v>1010</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>2877</v>
+        <v>2872</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>224</v>
@@ -14958,12 +14235,12 @@
         <v>1010</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>2877</v>
+        <v>2872</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>592</v>
@@ -14972,12 +14249,12 @@
         <v>1010</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>2877</v>
+        <v>2872</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>679</v>
@@ -14986,12 +14263,12 @@
         <v>1010</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>2878</v>
+        <v>2873</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>156</v>
@@ -15000,12 +14277,12 @@
         <v>1014</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>2878</v>
+        <v>2873</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>224</v>
@@ -15014,12 +14291,12 @@
         <v>1014</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>2878</v>
+        <v>2873</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>595</v>
@@ -15028,12 +14305,12 @@
         <v>1014</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>2878</v>
+        <v>2873</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>679</v>
@@ -15042,12 +14319,12 @@
         <v>1014</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>2879</v>
+        <v>2874</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>165</v>
@@ -15056,12 +14333,12 @@
         <v>1014</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>2879</v>
+        <v>2874</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>162</v>
@@ -15070,12 +14347,12 @@
         <v>1010</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>2879</v>
+        <v>2874</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>598</v>
@@ -15084,12 +14361,12 @@
         <v>1014</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>2879</v>
+        <v>2874</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>601</v>
@@ -15098,12 +14375,12 @@
         <v>1010</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>165</v>
@@ -15112,12 +14389,12 @@
         <v>1010</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>227</v>
@@ -15126,12 +14403,12 @@
         <v>1010</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>598</v>
@@ -15140,12 +14417,12 @@
         <v>1010</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>2880</v>
+        <v>2875</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>682</v>
@@ -15154,12 +14431,12 @@
         <v>1010</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>2881</v>
+        <v>2876</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>162</v>
@@ -15168,12 +14445,12 @@
         <v>1014</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>2881</v>
+        <v>2876</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>227</v>
@@ -15182,12 +14459,12 @@
         <v>1014</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>2881</v>
+        <v>2876</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>601</v>
@@ -15196,12 +14473,12 @@
         <v>1014</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>2881</v>
+        <v>2876</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>682</v>
@@ -15210,12 +14487,12 @@
         <v>1014</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>2882</v>
+        <v>2877</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>171</v>
@@ -15224,12 +14501,12 @@
         <v>1014</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>2882</v>
+        <v>2877</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>168</v>
@@ -15238,12 +14515,12 @@
         <v>1010</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>2882</v>
+        <v>2877</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>604</v>
@@ -15252,12 +14529,12 @@
         <v>1014</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>2882</v>
+        <v>2877</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>607</v>
@@ -15266,12 +14543,12 @@
         <v>1010</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>2883</v>
+        <v>2878</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>171</v>
@@ -15280,12 +14557,12 @@
         <v>1010</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>2883</v>
+        <v>2878</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>230</v>
@@ -15294,12 +14571,12 @@
         <v>1010</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>2883</v>
+        <v>2878</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>604</v>
@@ -15308,12 +14585,12 @@
         <v>1010</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>2883</v>
+        <v>2878</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>685</v>
@@ -15322,12 +14599,12 @@
         <v>1010</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>168</v>
@@ -15336,12 +14613,12 @@
         <v>1014</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>230</v>
@@ -15350,12 +14627,12 @@
         <v>1014</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>607</v>
@@ -15364,12 +14641,12 @@
         <v>1014</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>2884</v>
+        <v>2879</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>685</v>
@@ -15378,12 +14655,12 @@
         <v>1014</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>177</v>
@@ -15392,12 +14669,12 @@
         <v>1014</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>174</v>
@@ -15406,12 +14683,12 @@
         <v>1010</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>610</v>
@@ -15420,12 +14697,12 @@
         <v>1014</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>2885</v>
+        <v>2880</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>613</v>
@@ -15434,12 +14711,12 @@
         <v>1010</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>2886</v>
+        <v>2881</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>177</v>
@@ -15448,12 +14725,12 @@
         <v>1010</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>2886</v>
+        <v>2881</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>233</v>
@@ -15462,12 +14739,12 @@
         <v>1010</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>2886</v>
+        <v>2881</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>610</v>
@@ -15476,12 +14753,12 @@
         <v>1010</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>2886</v>
+        <v>2881</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>688</v>
@@ -15490,12 +14767,12 @@
         <v>1010</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>2887</v>
+        <v>2882</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>174</v>
@@ -15504,12 +14781,12 @@
         <v>1014</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>2887</v>
+        <v>2882</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>233</v>
@@ -15518,12 +14795,12 @@
         <v>1014</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>2887</v>
+        <v>2882</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>613</v>
@@ -15532,12 +14809,12 @@
         <v>1014</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>2887</v>
+        <v>2882</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>688</v>
@@ -15546,12 +14823,12 @@
         <v>1014</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>2888</v>
+        <v>2883</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>183</v>
@@ -15560,12 +14837,12 @@
         <v>1014</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>2888</v>
+        <v>2883</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>180</v>
@@ -15574,12 +14851,12 @@
         <v>1010</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>2888</v>
+        <v>2883</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>616</v>
@@ -15588,12 +14865,12 @@
         <v>1014</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>2888</v>
+        <v>2883</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>619</v>
@@ -15602,12 +14879,12 @@
         <v>1010</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>2889</v>
+        <v>2884</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>183</v>
@@ -15616,12 +14893,12 @@
         <v>1010</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>2889</v>
+        <v>2884</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>236</v>
@@ -15630,12 +14907,12 @@
         <v>1010</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>2889</v>
+        <v>2884</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>616</v>
@@ -15644,12 +14921,12 @@
         <v>1010</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>2889</v>
+        <v>2884</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>691</v>
@@ -15658,12 +14935,12 @@
         <v>1010</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>2890</v>
+        <v>2885</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>180</v>
@@ -15672,12 +14949,12 @@
         <v>1014</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>2890</v>
+        <v>2885</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>236</v>
@@ -15686,12 +14963,12 @@
         <v>1014</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>2890</v>
+        <v>2885</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>619</v>
@@ -15700,12 +14977,12 @@
         <v>1014</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>2890</v>
+        <v>2885</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>691</v>
@@ -15714,12 +14991,12 @@
         <v>1014</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>2891</v>
+        <v>2886</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>189</v>
@@ -15728,12 +15005,12 @@
         <v>1014</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>2891</v>
+        <v>2886</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>186</v>
@@ -15742,12 +15019,12 @@
         <v>1010</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>2891</v>
+        <v>2886</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>442</v>
@@ -15756,12 +15033,12 @@
         <v>1014</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>2891</v>
+        <v>2886</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>447</v>
@@ -15770,12 +15047,12 @@
         <v>1010</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>2892</v>
+        <v>2887</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>189</v>
@@ -15784,12 +15061,12 @@
         <v>1010</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>2892</v>
+        <v>2887</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>239</v>
@@ -15798,12 +15075,12 @@
         <v>1010</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>2892</v>
+        <v>2887</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>442</v>
@@ -15812,12 +15089,12 @@
         <v>1010</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>2892</v>
+        <v>2887</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>694</v>
@@ -15826,12 +15103,12 @@
         <v>1010</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>2893</v>
+        <v>2888</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>186</v>
@@ -15840,12 +15117,12 @@
         <v>1014</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>2893</v>
+        <v>2888</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>239</v>
@@ -15854,12 +15131,12 @@
         <v>1014</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>2893</v>
+        <v>2888</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>447</v>
@@ -15868,12 +15145,12 @@
         <v>1014</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>2893</v>
+        <v>2888</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>694</v>
@@ -15882,12 +15159,12 @@
         <v>1014</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>2894</v>
+        <v>2889</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>195</v>
@@ -15896,12 +15173,12 @@
         <v>1014</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>2894</v>
+        <v>2889</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>192</v>
@@ -15910,12 +15187,12 @@
         <v>1010</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>2894</v>
+        <v>2889</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>450</v>
@@ -15924,12 +15201,12 @@
         <v>1014</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>2894</v>
+        <v>2889</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>453</v>
@@ -15938,12 +15215,12 @@
         <v>1010</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>2895</v>
+        <v>2890</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>195</v>
@@ -15952,12 +15229,12 @@
         <v>1010</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>2895</v>
+        <v>2890</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>242</v>
@@ -15966,12 +15243,12 @@
         <v>1010</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>2895</v>
+        <v>2890</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>450</v>
@@ -15980,12 +15257,12 @@
         <v>1010</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>2895</v>
+        <v>2890</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>697</v>
@@ -15994,12 +15271,12 @@
         <v>1010</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>2896</v>
+        <v>2891</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>192</v>
@@ -16008,12 +15285,12 @@
         <v>1014</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>2861</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>2896</v>
+        <v>2891</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>242</v>
@@ -16022,12 +15299,12 @@
         <v>1014</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>2896</v>
+        <v>2891</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>453</v>
@@ -16036,12 +15313,12 @@
         <v>1014</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>2896</v>
+        <v>2891</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>697</v>
@@ -16050,7 +15327,7 @@
         <v>1014</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
     </row>
   </sheetData>
@@ -16084,16 +15361,16 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>2897</v>
+        <v>2892</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2318</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2898</v>
+        <v>2893</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2899</v>
+        <v>2894</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2460</v>
@@ -16102,28 +15379,28 @@
         <v>994</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>2895</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2896</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2696</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2897</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2898</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>2899</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>2900</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2901</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>2701</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>2902</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2903</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>2904</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>2905</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>2906</v>
       </c>
     </row>
   </sheetData>
@@ -35925,7 +35202,7 @@
     <col min="10" max="10" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>992</v>
       </c>
@@ -50124,7 +49401,7 @@
     <col min="9" max="9" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>2354</v>
       </c>
@@ -50266,7 +49543,7 @@
     <col min="11" max="11" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>2377</v>
       </c>
@@ -51197,7 +50474,7 @@
     <col min="6" max="6" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>2459</v>
       </c>

--- a/Locks_and_deferred.xlsx
+++ b/Locks_and_deferred.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cesar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D63A9F-5B2A-45B6-9608-F380C33D8DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D016B0A-E951-4735-B959-DC4D1D140979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9431,16 +9431,16 @@
         <v>2073</v>
       </c>
       <c r="F2" s="4">
-        <v>1036</v>
+        <v>1053</v>
       </c>
       <c r="G2" s="4">
-        <v>1036</v>
+        <v>1176</v>
       </c>
       <c r="H2" s="4">
-        <v>1100</v>
+        <v>910</v>
       </c>
       <c r="I2" s="4">
-        <v>1100</v>
+        <v>1086</v>
       </c>
       <c r="J2" t="s">
         <v>6</v>
@@ -9463,7 +9463,7 @@
         <v>3701</v>
       </c>
       <c r="F3" s="4">
-        <v>1746</v>
+        <v>1718</v>
       </c>
       <c r="G3" s="4">
         <v>1747</v>
@@ -9533,10 +9533,10 @@
         <v>1747</v>
       </c>
       <c r="H5" s="4">
-        <v>1760</v>
+        <v>2105</v>
       </c>
       <c r="I5" s="4">
-        <v>1916</v>
+        <v>1750</v>
       </c>
       <c r="J5" t="s">
         <v>6</v>
@@ -9565,10 +9565,10 @@
         <v>1747</v>
       </c>
       <c r="H6" s="4">
-        <v>1916</v>
+        <v>1751</v>
       </c>
       <c r="I6" s="4">
-        <v>1968</v>
+        <v>2106</v>
       </c>
       <c r="J6" t="s">
         <v>6</v>
@@ -9597,10 +9597,10 @@
         <v>1747</v>
       </c>
       <c r="H7" s="4">
-        <v>1760</v>
+        <v>2176</v>
       </c>
       <c r="I7" s="4">
-        <v>1916</v>
+        <v>2147</v>
       </c>
       <c r="J7" t="s">
         <v>6</v>
@@ -9629,10 +9629,10 @@
         <v>1747</v>
       </c>
       <c r="H8" s="4">
-        <v>1916</v>
+        <v>2146</v>
       </c>
       <c r="I8" s="4">
-        <v>1968</v>
+        <v>2182</v>
       </c>
       <c r="J8" t="s">
         <v>6</v>
@@ -9661,10 +9661,10 @@
         <v>1747</v>
       </c>
       <c r="H9" s="4">
-        <v>1760</v>
+        <v>2056</v>
       </c>
       <c r="I9" s="4">
-        <v>1916</v>
+        <v>2057</v>
       </c>
       <c r="J9" t="s">
         <v>6</v>
@@ -9693,10 +9693,10 @@
         <v>1747</v>
       </c>
       <c r="H10" s="4">
-        <v>1916</v>
+        <v>2056</v>
       </c>
       <c r="I10" s="4">
-        <v>1968</v>
+        <v>2057</v>
       </c>
       <c r="J10" t="s">
         <v>6</v>
@@ -9716,19 +9716,19 @@
         <v>159</v>
       </c>
       <c r="E11" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F11" s="4">
-        <v>1746</v>
+        <v>2466</v>
       </c>
       <c r="G11" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H11" s="4">
-        <v>1760</v>
+        <v>3076</v>
       </c>
       <c r="I11" s="4">
-        <v>1916</v>
+        <v>2890</v>
       </c>
       <c r="J11" t="s">
         <v>6</v>
@@ -9748,19 +9748,19 @@
         <v>156</v>
       </c>
       <c r="E12" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F12" s="4">
-        <v>1746</v>
+        <v>2466</v>
       </c>
       <c r="G12" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H12" s="4">
-        <v>1916</v>
+        <v>2962</v>
       </c>
       <c r="I12" s="4">
-        <v>1968</v>
+        <v>3077</v>
       </c>
       <c r="J12" t="s">
         <v>6</v>
@@ -9780,19 +9780,19 @@
         <v>165</v>
       </c>
       <c r="E13" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F13" s="4">
-        <v>1746</v>
+        <v>2399</v>
       </c>
       <c r="G13" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H13" s="4">
-        <v>1760</v>
+        <v>2993</v>
       </c>
       <c r="I13" s="4">
-        <v>1916</v>
+        <v>2741</v>
       </c>
       <c r="J13" t="s">
         <v>6</v>
@@ -9812,19 +9812,19 @@
         <v>162</v>
       </c>
       <c r="E14" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F14" s="4">
-        <v>1746</v>
+        <v>2399</v>
       </c>
       <c r="G14" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H14" s="4">
-        <v>1916</v>
+        <v>2740</v>
       </c>
       <c r="I14" s="4">
-        <v>1968</v>
+        <v>2993</v>
       </c>
       <c r="J14" t="s">
         <v>6</v>
@@ -9847,16 +9847,16 @@
         <v>3701</v>
       </c>
       <c r="F15" s="4">
-        <v>1746</v>
+        <v>1700</v>
       </c>
       <c r="G15" s="4">
         <v>1747</v>
       </c>
       <c r="H15" s="4">
-        <v>1760</v>
+        <v>2077</v>
       </c>
       <c r="I15" s="4">
-        <v>1916</v>
+        <v>2076</v>
       </c>
       <c r="J15" t="s">
         <v>6</v>
@@ -9879,16 +9879,16 @@
         <v>3701</v>
       </c>
       <c r="F16" s="4">
-        <v>1746</v>
+        <v>1700</v>
       </c>
       <c r="G16" s="4">
         <v>1747</v>
       </c>
       <c r="H16" s="4">
-        <v>1916</v>
+        <v>2075</v>
       </c>
       <c r="I16" s="4">
-        <v>1968</v>
+        <v>2077</v>
       </c>
       <c r="J16" t="s">
         <v>6</v>
@@ -9917,10 +9917,10 @@
         <v>1747</v>
       </c>
       <c r="H17" s="4">
-        <v>1760</v>
+        <v>2011</v>
       </c>
       <c r="I17" s="4">
-        <v>1916</v>
+        <v>2011</v>
       </c>
       <c r="J17" t="s">
         <v>6</v>
@@ -9949,10 +9949,10 @@
         <v>1747</v>
       </c>
       <c r="H18" s="4">
-        <v>1916</v>
+        <v>2011</v>
       </c>
       <c r="I18" s="4">
-        <v>1968</v>
+        <v>2011</v>
       </c>
       <c r="J18" t="s">
         <v>6</v>
@@ -9981,10 +9981,10 @@
         <v>1747</v>
       </c>
       <c r="H19" s="4">
-        <v>1760</v>
+        <v>2104</v>
       </c>
       <c r="I19" s="4">
-        <v>1916</v>
+        <v>2105</v>
       </c>
       <c r="J19" t="s">
         <v>6</v>
@@ -10013,10 +10013,10 @@
         <v>1747</v>
       </c>
       <c r="H20" s="4">
-        <v>1916</v>
+        <v>2104</v>
       </c>
       <c r="I20" s="4">
-        <v>1968</v>
+        <v>2105</v>
       </c>
       <c r="J20" t="s">
         <v>6</v>
@@ -10045,10 +10045,10 @@
         <v>1747</v>
       </c>
       <c r="H21" s="4">
-        <v>1760</v>
+        <v>2170</v>
       </c>
       <c r="I21" s="4">
-        <v>1916</v>
+        <v>2171</v>
       </c>
       <c r="J21" t="s">
         <v>6</v>
@@ -10077,10 +10077,10 @@
         <v>1747</v>
       </c>
       <c r="H22" s="4">
-        <v>1916</v>
+        <v>2170</v>
       </c>
       <c r="I22" s="4">
-        <v>1968</v>
+        <v>2171</v>
       </c>
       <c r="J22" t="s">
         <v>6</v>
@@ -10112,7 +10112,7 @@
         <v>1997</v>
       </c>
       <c r="I23" s="4">
-        <v>1916</v>
+        <v>2015</v>
       </c>
       <c r="J23" t="s">
         <v>6</v>
@@ -10141,10 +10141,10 @@
         <v>1747</v>
       </c>
       <c r="H24" s="4">
-        <v>1916</v>
+        <v>2014</v>
       </c>
       <c r="I24" s="4">
-        <v>1968</v>
+        <v>1998</v>
       </c>
       <c r="J24" t="s">
         <v>6</v>
@@ -10164,19 +10164,19 @@
         <v>198</v>
       </c>
       <c r="E25" s="4">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="F25" s="4">
-        <v>2721</v>
+        <v>1609</v>
       </c>
       <c r="G25" s="4">
-        <v>2721</v>
+        <v>1609</v>
       </c>
       <c r="H25" s="4">
-        <v>1133</v>
+        <v>1253</v>
       </c>
       <c r="I25" s="4">
-        <v>1133</v>
+        <v>1253</v>
       </c>
       <c r="J25" t="s">
         <v>6</v>
@@ -10196,19 +10196,19 @@
         <v>1</v>
       </c>
       <c r="E26" s="4">
-        <v>2280</v>
+        <v>2073</v>
       </c>
       <c r="F26" s="4">
-        <v>1140</v>
+        <v>1053</v>
       </c>
       <c r="G26" s="4">
-        <v>1140</v>
+        <v>1176</v>
       </c>
       <c r="H26" s="4">
-        <v>1200</v>
+        <v>910</v>
       </c>
       <c r="I26" s="4">
-        <v>1200</v>
+        <v>1086</v>
       </c>
       <c r="J26" t="s">
         <v>6</v>
@@ -10231,7 +10231,7 @@
         <v>3701</v>
       </c>
       <c r="F27" s="4">
-        <v>1746</v>
+        <v>1718</v>
       </c>
       <c r="G27" s="4">
         <v>1747</v>
@@ -10301,10 +10301,10 @@
         <v>1747</v>
       </c>
       <c r="H29" s="4">
-        <v>1760</v>
+        <v>2105</v>
       </c>
       <c r="I29" s="4">
-        <v>1916</v>
+        <v>1750</v>
       </c>
       <c r="J29" t="s">
         <v>6</v>
@@ -10333,10 +10333,10 @@
         <v>1747</v>
       </c>
       <c r="H30" s="4">
-        <v>1916</v>
+        <v>1751</v>
       </c>
       <c r="I30" s="4">
-        <v>1968</v>
+        <v>2106</v>
       </c>
       <c r="J30" t="s">
         <v>6</v>
@@ -10365,10 +10365,10 @@
         <v>1747</v>
       </c>
       <c r="H31" s="4">
-        <v>1760</v>
+        <v>2176</v>
       </c>
       <c r="I31" s="4">
-        <v>1916</v>
+        <v>2147</v>
       </c>
       <c r="J31" t="s">
         <v>6</v>
@@ -10397,10 +10397,10 @@
         <v>1747</v>
       </c>
       <c r="H32" s="4">
-        <v>1916</v>
+        <v>2146</v>
       </c>
       <c r="I32" s="4">
-        <v>1968</v>
+        <v>2182</v>
       </c>
       <c r="J32" t="s">
         <v>6</v>
@@ -10429,10 +10429,10 @@
         <v>1747</v>
       </c>
       <c r="H33" s="4">
-        <v>1760</v>
+        <v>2056</v>
       </c>
       <c r="I33" s="4">
-        <v>1916</v>
+        <v>2057</v>
       </c>
       <c r="J33" t="s">
         <v>6</v>
@@ -10461,10 +10461,10 @@
         <v>1747</v>
       </c>
       <c r="H34" s="4">
-        <v>1916</v>
+        <v>2056</v>
       </c>
       <c r="I34" s="4">
-        <v>1968</v>
+        <v>2057</v>
       </c>
       <c r="J34" t="s">
         <v>6</v>
@@ -10484,19 +10484,19 @@
         <v>592</v>
       </c>
       <c r="E35" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F35" s="4">
-        <v>1746</v>
+        <v>2466</v>
       </c>
       <c r="G35" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H35" s="4">
-        <v>1760</v>
+        <v>3076</v>
       </c>
       <c r="I35" s="4">
-        <v>1916</v>
+        <v>2890</v>
       </c>
       <c r="J35" t="s">
         <v>6</v>
@@ -10516,19 +10516,19 @@
         <v>595</v>
       </c>
       <c r="E36" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F36" s="4">
-        <v>1746</v>
+        <v>2466</v>
       </c>
       <c r="G36" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H36" s="4">
-        <v>1916</v>
+        <v>2962</v>
       </c>
       <c r="I36" s="4">
-        <v>1968</v>
+        <v>3077</v>
       </c>
       <c r="J36" t="s">
         <v>6</v>
@@ -10548,19 +10548,19 @@
         <v>598</v>
       </c>
       <c r="E37" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F37" s="4">
-        <v>1746</v>
+        <v>2399</v>
       </c>
       <c r="G37" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H37" s="4">
-        <v>1760</v>
+        <v>2993</v>
       </c>
       <c r="I37" s="4">
-        <v>1916</v>
+        <v>2741</v>
       </c>
       <c r="J37" t="s">
         <v>6</v>
@@ -10580,19 +10580,19 @@
         <v>601</v>
       </c>
       <c r="E38" s="4">
-        <v>3701</v>
+        <v>5225</v>
       </c>
       <c r="F38" s="4">
-        <v>1746</v>
+        <v>2399</v>
       </c>
       <c r="G38" s="4">
-        <v>1747</v>
+        <v>2400</v>
       </c>
       <c r="H38" s="4">
-        <v>1916</v>
+        <v>2740</v>
       </c>
       <c r="I38" s="4">
-        <v>1968</v>
+        <v>2993</v>
       </c>
       <c r="J38" t="s">
         <v>6</v>
@@ -10615,16 +10615,16 @@
         <v>3701</v>
       </c>
       <c r="F39" s="4">
-        <v>1746</v>
+        <v>1700</v>
       </c>
       <c r="G39" s="4">
         <v>1747</v>
       </c>
       <c r="H39" s="4">
-        <v>1760</v>
+        <v>2077</v>
       </c>
       <c r="I39" s="4">
-        <v>1916</v>
+        <v>2076</v>
       </c>
       <c r="J39" t="s">
         <v>6</v>
@@ -10647,16 +10647,16 @@
         <v>3701</v>
       </c>
       <c r="F40" s="4">
-        <v>1746</v>
+        <v>1700</v>
       </c>
       <c r="G40" s="4">
         <v>1747</v>
       </c>
       <c r="H40" s="4">
-        <v>1916</v>
+        <v>2075</v>
       </c>
       <c r="I40" s="4">
-        <v>1968</v>
+        <v>2077</v>
       </c>
       <c r="J40" t="s">
         <v>6</v>
@@ -10685,10 +10685,10 @@
         <v>1747</v>
       </c>
       <c r="H41" s="4">
-        <v>1760</v>
+        <v>2011</v>
       </c>
       <c r="I41" s="4">
-        <v>1916</v>
+        <v>2011</v>
       </c>
       <c r="J41" t="s">
         <v>6</v>
@@ -10717,10 +10717,10 @@
         <v>1747</v>
       </c>
       <c r="H42" s="4">
-        <v>1916</v>
+        <v>2011</v>
       </c>
       <c r="I42" s="4">
-        <v>1968</v>
+        <v>2011</v>
       </c>
       <c r="J42" t="s">
         <v>6</v>
@@ -10749,10 +10749,10 @@
         <v>1747</v>
       </c>
       <c r="H43" s="4">
-        <v>1760</v>
+        <v>2104</v>
       </c>
       <c r="I43" s="4">
-        <v>1916</v>
+        <v>2105</v>
       </c>
       <c r="J43" t="s">
         <v>6</v>
@@ -10781,10 +10781,10 @@
         <v>1747</v>
       </c>
       <c r="H44" s="4">
-        <v>1916</v>
+        <v>2104</v>
       </c>
       <c r="I44" s="4">
-        <v>1968</v>
+        <v>2105</v>
       </c>
       <c r="J44" t="s">
         <v>6</v>
@@ -10813,10 +10813,10 @@
         <v>1747</v>
       </c>
       <c r="H45" s="4">
-        <v>1760</v>
+        <v>2170</v>
       </c>
       <c r="I45" s="4">
-        <v>1916</v>
+        <v>2171</v>
       </c>
       <c r="J45" t="s">
         <v>6</v>
@@ -10845,10 +10845,10 @@
         <v>1747</v>
       </c>
       <c r="H46" s="4">
-        <v>1916</v>
+        <v>2170</v>
       </c>
       <c r="I46" s="4">
-        <v>1968</v>
+        <v>2171</v>
       </c>
       <c r="J46" t="s">
         <v>6</v>
@@ -10877,10 +10877,10 @@
         <v>1747</v>
       </c>
       <c r="H47" s="4">
-        <v>1850</v>
+        <v>1997</v>
       </c>
       <c r="I47" s="4">
-        <v>1916</v>
+        <v>2015</v>
       </c>
       <c r="J47" t="s">
         <v>6</v>
@@ -10909,10 +10909,10 @@
         <v>1747</v>
       </c>
       <c r="H48" s="4">
-        <v>1916</v>
+        <v>2014</v>
       </c>
       <c r="I48" s="4">
-        <v>1968</v>
+        <v>1998</v>
       </c>
       <c r="J48" t="s">
         <v>6</v>
@@ -10932,19 +10932,19 @@
         <v>17</v>
       </c>
       <c r="E49" s="4">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="F49" s="4">
-        <v>2721</v>
+        <v>1609</v>
       </c>
       <c r="G49" s="4">
-        <v>2721</v>
+        <v>1609</v>
       </c>
       <c r="H49" s="4">
-        <v>1133</v>
+        <v>1253</v>
       </c>
       <c r="I49" s="4">
-        <v>1133</v>
+        <v>1253</v>
       </c>
       <c r="J49" t="s">
         <v>6</v>
